--- a/example_data/data_sum/electroopitcal.xlsx
+++ b/example_data/data_sum/electroopitcal.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70942\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C30A63D-41D8-46F5-A469-55DB5681F34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,90 +27,86 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B3LYP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBE0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M062X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wb97xd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cam-B3LYP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCF-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCF-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCF-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">230-b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1-ON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F2-ON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F3-ON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3-ON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JRD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZ-FTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">245-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">245-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>B3LYP</t>
+  </si>
+  <si>
+    <t>PBE0</t>
+  </si>
+  <si>
+    <t>M062X</t>
+  </si>
+  <si>
+    <t>wb97xd</t>
+  </si>
+  <si>
+    <t>cam-B3LYP</t>
+  </si>
+  <si>
+    <t>MP2</t>
+  </si>
+  <si>
+    <t>TCF-1</t>
+  </si>
+  <si>
+    <t>TCF-2</t>
+  </si>
+  <si>
+    <t>TCF-3</t>
+  </si>
+  <si>
+    <t>230-b</t>
+  </si>
+  <si>
+    <t>F1-ON</t>
+  </si>
+  <si>
+    <t>F2-ON</t>
+  </si>
+  <si>
+    <t>F3-ON</t>
+  </si>
+  <si>
+    <t>M3-ON</t>
+  </si>
+  <si>
+    <t>JRD1</t>
+  </si>
+  <si>
+    <t>EZ-FTC</t>
+  </si>
+  <si>
+    <t>245-5</t>
+  </si>
+  <si>
+    <t>245-8</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -115,28 +116,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -149,6 +135,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -159,7 +151,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -167,96 +159,350 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:O39"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AMJ39"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.88"/>
+    <col min="1" max="1024" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -291,32 +537,32 @@
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="3">
         <v>1330</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="4">
         <v>408.77</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="4">
         <v>405.3</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="4">
         <v>444.09</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="4">
         <v>386.95</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="4">
         <v>414.85</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="4">
         <v>160.72</v>
       </c>
       <c r="J2" s="3"/>
@@ -326,32 +572,32 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="3">
         <v>2540</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="3">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>1460.82</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="4">
         <v>1393.93</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="4">
         <v>1362.28</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>1055.61</v>
-      </c>
-      <c r="H3" s="4" t="n">
+      <c r="G3" s="4">
+        <v>1055.6099999999999</v>
+      </c>
+      <c r="H3" s="4">
         <v>1250.47</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="4">
         <v>420.89</v>
       </c>
       <c r="J3" s="3"/>
@@ -361,32 +607,32 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:15">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3">
         <v>2310</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>6447.04</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="4">
         <v>5166.5</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4">
         <v>3661.74</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="4">
         <v>2400.39</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="4">
         <v>3298.31</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="4">
         <v>923.27</v>
       </c>
       <c r="J4" s="3"/>
@@ -396,32 +642,32 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:15" s="7" customFormat="1" ht="12.45">
       <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="5">
         <v>2654</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="6">
         <v>2412.59</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="6">
         <v>3955.47</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>20179.49</v>
-      </c>
-      <c r="G5" s="6" t="n">
+      <c r="F5" s="6">
+        <v>20179.490000000002</v>
+      </c>
+      <c r="G5" s="6">
         <v>10608.2</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="6">
         <v>2664.96</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="6">
         <v>935.46</v>
       </c>
       <c r="J5" s="5"/>
@@ -431,32 +677,32 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:15" s="7" customFormat="1" ht="12.45">
       <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="5">
         <v>1815</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="6">
         <v>724.21</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="6">
         <v>790.63</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="6">
         <v>1324.86</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="6">
         <v>1455.6</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <v>1274.1</v>
-      </c>
-      <c r="I6" s="6" t="n">
+      <c r="H6" s="6">
+        <v>1274.0999999999999</v>
+      </c>
+      <c r="I6" s="6">
         <v>760.05</v>
       </c>
       <c r="J6" s="5"/>
@@ -466,25 +712,25 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:15" s="7" customFormat="1" ht="12.45">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="5">
         <v>1495</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="5">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="6">
         <v>961.3</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="6">
         <v>1760.3</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="6">
         <v>1526.31</v>
       </c>
       <c r="I7" s="6"/>
@@ -495,27 +741,27 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:15" s="7" customFormat="1" ht="12.45">
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="5">
         <v>3797</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="5">
         <v>3</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="6">
         <v>790.35</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="6">
         <v>951.93</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="6">
         <v>1948.6</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="6">
         <v>1925.62</v>
       </c>
       <c r="I8" s="6"/>
@@ -526,24 +772,24 @@
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:15" s="7" customFormat="1" ht="12.45">
       <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="5">
         <v>3879</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="5">
         <v>3</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="6">
         <v>1927.05</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="6">
         <v>2025.46</v>
       </c>
       <c r="F9" s="6"/>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="6">
         <v>1792.15</v>
       </c>
       <c r="H9" s="6"/>
@@ -555,30 +801,30 @@
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="3">
         <v>1680</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="3">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>1049.45</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>1101.87</v>
-      </c>
-      <c r="F10" s="4" t="n">
+      <c r="E10" s="4">
+        <v>1101.8699999999999</v>
+      </c>
+      <c r="F10" s="4">
         <v>1349.52</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4">
         <v>1204.98</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>1233.59</v>
+      <c r="H10" s="4">
+        <v>1233.5899999999999</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="3"/>
@@ -588,32 +834,32 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="3">
         <v>450</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="3">
         <v>4</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>593</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4">
         <v>604.65</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>603.81</v>
-      </c>
-      <c r="G11" s="4" t="n">
+      <c r="F11" s="4">
+        <v>603.80999999999995</v>
+      </c>
+      <c r="G11" s="4">
         <v>459.5</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="4">
         <v>478.6</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="4">
         <v>218.14</v>
       </c>
       <c r="J11" s="3"/>
@@ -623,32 +869,32 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:15">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="3">
         <v>360</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="3">
         <v>5</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>25.93</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="4">
         <v>15.72</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="4">
         <v>54.04</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="4">
         <v>115.48</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="4">
         <v>39.92</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="4">
         <v>12.89</v>
       </c>
       <c r="J12" s="3"/>
@@ -658,32 +904,32 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="3">
         <v>560</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="3">
         <v>5</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>25.92</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>211.12</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>356.94</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>181.35</v>
-      </c>
-      <c r="I13" s="4" t="n">
+      <c r="D13" s="4">
+        <v>33</v>
+      </c>
+      <c r="E13" s="4">
+        <v>53</v>
+      </c>
+      <c r="F13" s="4">
+        <v>224</v>
+      </c>
+      <c r="G13" s="4">
+        <v>368</v>
+      </c>
+      <c r="H13" s="4">
+        <v>193</v>
+      </c>
+      <c r="I13" s="4">
         <v>125</v>
       </c>
       <c r="J13" s="3"/>
@@ -692,32 +938,32 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="3">
         <v>105.72</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="3">
         <v>6</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>233.9698599</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>217.5151121</v>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="D14" s="4">
+        <v>233.96985989999999</v>
+      </c>
+      <c r="E14" s="8">
+        <v>217.51511210000001</v>
+      </c>
+      <c r="F14" s="8">
         <v>164.3015446</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="8">
         <v>163.2373312</v>
       </c>
-      <c r="H14" s="8" t="n">
-        <v>131.7867892</v>
-      </c>
-      <c r="I14" s="4" t="n">
+      <c r="H14" s="8">
+        <v>131.78678919999999</v>
+      </c>
+      <c r="I14" s="4">
         <v>84.65</v>
       </c>
       <c r="J14" s="3"/>
@@ -727,33 +973,33 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="3">
         <v>86.62</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="3">
         <v>6</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>170.3539603</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>158.1044898</v>
-      </c>
-      <c r="F15" s="8" t="n">
+      <c r="D15" s="4">
+        <v>170.35396030000001</v>
+      </c>
+      <c r="E15" s="8">
+        <v>158.10448980000001</v>
+      </c>
+      <c r="F15" s="8">
         <v>120.501402</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="8">
         <v>122.9810325</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>100.4308955</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>66.99</v>
+      <c r="H15" s="8">
+        <v>100.43089550000001</v>
+      </c>
+      <c r="I15" s="4">
+        <v>66.989999999999995</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -761,32 +1007,32 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:15">
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="3">
         <v>71.89</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>144.6873507</v>
       </c>
-      <c r="E16" s="8" t="n">
-        <v>133.6547398</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>97.82402749</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>102.1534591</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>82.81639336</v>
-      </c>
-      <c r="I16" s="4" t="n">
+      <c r="E16" s="8">
+        <v>133.65473979999999</v>
+      </c>
+      <c r="F16" s="8">
+        <v>97.824027490000006</v>
+      </c>
+      <c r="G16" s="8">
+        <v>102.15345910000001</v>
+      </c>
+      <c r="H16" s="8">
+        <v>82.816393360000006</v>
+      </c>
+      <c r="I16" s="4">
         <v>53.39</v>
       </c>
       <c r="J16" s="3"/>
@@ -795,32 +1041,32 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:15">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>66.65</v>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="B17" s="3">
+        <v>66.650000000000006</v>
+      </c>
+      <c r="C17" s="3">
         <v>6</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>124.782613</v>
       </c>
-      <c r="E17" s="8" t="n">
-        <v>115.2416687</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>85.72265795</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>90.01749426</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>73.35558491</v>
-      </c>
-      <c r="I17" s="4" t="n">
+      <c r="E17" s="8">
+        <v>115.24166870000001</v>
+      </c>
+      <c r="F17" s="8">
+        <v>85.722657949999999</v>
+      </c>
+      <c r="G17" s="8">
+        <v>90.017494260000007</v>
+      </c>
+      <c r="H17" s="8">
+        <v>73.355584910000005</v>
+      </c>
+      <c r="I17" s="4">
         <v>48.66</v>
       </c>
       <c r="J17" s="3"/>
@@ -829,32 +1075,32 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:15">
       <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="3">
         <v>2654</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="3">
         <v>7</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>2412.59</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="4">
         <v>3955.47</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>20179.49</v>
-      </c>
-      <c r="G18" s="4" t="n">
+      <c r="F18" s="4">
+        <v>20179.490000000002</v>
+      </c>
+      <c r="G18" s="4">
         <v>10608.2</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="4">
         <v>2664.96</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="4">
         <v>935.46</v>
       </c>
       <c r="J18" s="3"/>
@@ -864,29 +1110,29 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:15">
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="3">
         <v>3300</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="3">
         <v>7</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>4596.05</v>
       </c>
-      <c r="E19" s="4" t="n">
-        <v>9505.63</v>
-      </c>
-      <c r="F19" s="4" t="n">
+      <c r="E19" s="4">
+        <v>9505.6299999999992</v>
+      </c>
+      <c r="F19" s="4">
         <v>52415.66</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="4">
         <v>10914.11</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="4">
         <v>32097.47</v>
       </c>
       <c r="I19" s="3"/>
@@ -897,32 +1143,32 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:15">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="3">
         <v>3600</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="3">
         <v>7</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>4290</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="4">
         <v>9738</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="4">
         <v>6156</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="4">
         <v>2226</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="4">
         <v>3131</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="3">
         <v>620</v>
       </c>
       <c r="J20" s="3"/>
@@ -931,7 +1177,7 @@
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:15">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -947,23 +1193,17 @@
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:15">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:15">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -980,7 +1220,7 @@
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:15">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -997,7 +1237,7 @@
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:15">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1014,7 +1254,7 @@
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:15">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1031,7 +1271,7 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:15">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1048,7 +1288,7 @@
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:15">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1065,7 +1305,7 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:15">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1082,7 +1322,7 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:15">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1099,7 +1339,7 @@
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:15">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1116,7 +1356,7 @@
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:15">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1133,7 +1373,7 @@
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:15">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1150,7 +1390,7 @@
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:15">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1167,7 +1407,7 @@
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:15">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1184,7 +1424,7 @@
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:15">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1201,7 +1441,7 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:15">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1218,7 +1458,7 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:15">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1235,7 +1475,7 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:15">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1253,12 +1493,8 @@
       <c r="O39" s="3"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/example_data/data_sum/electroopitcal.xlsx
+++ b/example_data/data_sum/electroopitcal.xlsx
@@ -1,31 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70942\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\70942\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EB26C8-9374-47AD-9BAE-DAD75DBCF601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B4FBDD-12EC-48C4-83C8-56ED5D7F9B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11923" yWindow="8006" windowWidth="19911" windowHeight="12223" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>B3LYP</t>
+  </si>
+  <si>
+    <t>PBE0</t>
+  </si>
+  <si>
+    <t>M062X</t>
+  </si>
+  <si>
+    <t>wb97xd</t>
+  </si>
+  <si>
+    <t>cam-B3LYP</t>
+  </si>
+  <si>
+    <t>MP2</t>
+  </si>
   <si>
     <t>TCF-1</t>
   </si>
@@ -36,9 +63,6 @@
     <t>TCF-3</t>
   </si>
   <si>
-    <t>230-b</t>
-  </si>
-  <si>
     <t>F1-ON</t>
   </si>
   <si>
@@ -57,88 +81,66 @@
     <t>EZ-FTC</t>
   </si>
   <si>
-    <t>245-5</t>
-  </si>
-  <si>
-    <t>245-8</t>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>exp</t>
-  </si>
-  <si>
-    <t>source</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>P1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>P3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>P4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>P5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B3LYP</t>
-  </si>
-  <si>
-    <t>PBE0</t>
-  </si>
-  <si>
-    <t>M062X</t>
-  </si>
-  <si>
-    <t>wb97xd</t>
-  </si>
-  <si>
-    <t>cam-B3LYP</t>
-  </si>
-  <si>
-    <t>MP2</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CDF[3]MePy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDF[3]HMQ </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,15 +163,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -188,7 +201,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -204,7 +217,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -216,7 +229,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -233,7 +246,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -263,12 +276,29 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -298,6 +328,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -450,39 +497,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O39"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <dimension ref="A1:AMJ39"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1024" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -493,7 +540,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3">
         <v>1330</v>
@@ -501,22 +548,22 @@
       <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>408.77</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>405.3</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="4">
         <v>444.09</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <v>386.95</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="4">
         <v>414.85</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="4">
         <v>160.72</v>
       </c>
       <c r="J2" s="3"/>
@@ -528,7 +575,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3">
         <v>2540</v>
@@ -536,22 +583,22 @@
       <c r="C3" s="3">
         <v>1</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>1460.82</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>1393.93</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>1362.28</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="4">
         <v>1055.6099999999999</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>1250.47</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <v>420.89</v>
       </c>
       <c r="J3" s="3"/>
@@ -563,7 +610,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3">
         <v>2310</v>
@@ -571,22 +618,22 @@
       <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>6447.04</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>5166.5</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>3661.74</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <v>2400.39</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <v>3298.31</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="4">
         <v>923.27</v>
       </c>
       <c r="J4" s="3"/>
@@ -596,168 +643,168 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:15" s="7" customFormat="1" ht="12.45">
+      <c r="A5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2654</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6">
+        <v>2412.59</v>
+      </c>
+      <c r="E5" s="6">
+        <v>3955.47</v>
+      </c>
+      <c r="F5" s="6">
+        <v>20179.490000000002</v>
+      </c>
+      <c r="G5" s="6">
+        <v>10608.2</v>
+      </c>
+      <c r="H5" s="6">
+        <v>2664.96</v>
+      </c>
+      <c r="I5" s="6">
+        <v>935.46</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" s="7" customFormat="1" ht="12.45">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1815</v>
+      </c>
+      <c r="C6" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
-        <v>2654</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2412.59</v>
-      </c>
-      <c r="E5" s="3">
-        <v>3955.47</v>
-      </c>
-      <c r="F5" s="3">
-        <v>20179.490000000002</v>
-      </c>
-      <c r="G5" s="3">
-        <v>10608.2</v>
-      </c>
-      <c r="H5" s="3">
-        <v>2664.96</v>
-      </c>
-      <c r="I5" s="3">
-        <v>935.46</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1815</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="D6" s="6">
+        <v>724.21</v>
+      </c>
+      <c r="E6" s="6">
+        <v>790.63</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1324.86</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1455.6</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1274.0999999999999</v>
+      </c>
+      <c r="I6" s="6">
+        <v>760.05</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" s="7" customFormat="1" ht="12.45">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1495</v>
+      </c>
+      <c r="C7" s="5">
         <v>3</v>
       </c>
-      <c r="D6" s="3">
-        <v>724.21</v>
-      </c>
-      <c r="E6" s="3">
-        <v>790.63</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1324.86</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1455.6</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1274.0999999999999</v>
-      </c>
-      <c r="I6" s="3">
-        <v>760.05</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1495</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="D7" s="6">
+        <v>961.3</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6">
+        <v>1760.3</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1526.31</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" s="7" customFormat="1" ht="12.45">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3797</v>
+      </c>
+      <c r="C8" s="5">
         <v>3</v>
       </c>
-      <c r="D7" s="3">
-        <v>961.3</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3">
-        <v>1760.3</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1526.31</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3">
-        <v>3797</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="D8" s="6">
+        <v>790.35</v>
+      </c>
+      <c r="E8" s="6">
+        <v>951.93</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1948.6</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6">
+        <v>1925.62</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" s="7" customFormat="1" ht="12.45">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3879</v>
+      </c>
+      <c r="C9" s="5">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>790.35</v>
-      </c>
-      <c r="E8" s="3">
-        <v>951.93</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1948.6</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>1925.62</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3">
-        <v>3879</v>
-      </c>
-      <c r="C9" s="3">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="D9" s="6">
         <v>1927.05</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="6">
         <v>2025.46</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3">
+      <c r="F9" s="6"/>
+      <c r="G9" s="6">
         <v>1792.15</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3">
         <v>1680</v>
@@ -765,22 +812,22 @@
       <c r="C10" s="3">
         <v>4</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>1049.45</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>1101.8699999999999</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>1349.52</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>1204.98</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>1233.5899999999999</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="4"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -790,7 +837,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B11" s="3">
         <v>450</v>
@@ -798,22 +845,22 @@
       <c r="C11" s="3">
         <v>4</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>593</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <v>604.65</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>603.80999999999995</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>459.5</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <v>478.6</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <v>218.14</v>
       </c>
       <c r="J11" s="3"/>
@@ -825,7 +872,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3">
         <v>360</v>
@@ -833,22 +880,22 @@
       <c r="C12" s="3">
         <v>5</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>25.93</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>15.72</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>54.04</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>115.48</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>39.92</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>12.89</v>
       </c>
       <c r="J12" s="3"/>
@@ -860,7 +907,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3">
         <v>560</v>
@@ -868,22 +915,22 @@
       <c r="C13" s="3">
         <v>5</v>
       </c>
-      <c r="D13" s="3">
-        <v>25.92</v>
-      </c>
-      <c r="E13" s="3">
-        <v>46.05</v>
-      </c>
-      <c r="F13" s="3">
-        <v>211.12</v>
-      </c>
-      <c r="G13" s="3">
-        <v>356.94</v>
-      </c>
-      <c r="H13" s="3">
-        <v>181.35</v>
-      </c>
-      <c r="I13" s="3">
+      <c r="D13" s="4">
+        <v>33</v>
+      </c>
+      <c r="E13" s="4">
+        <v>53</v>
+      </c>
+      <c r="F13" s="4">
+        <v>224</v>
+      </c>
+      <c r="G13" s="4">
+        <v>368</v>
+      </c>
+      <c r="H13" s="4">
+        <v>193</v>
+      </c>
+      <c r="I13" s="4">
         <v>125</v>
       </c>
       <c r="J13" s="3"/>
@@ -894,7 +941,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B14" s="3">
         <v>105.72</v>
@@ -902,22 +949,22 @@
       <c r="C14" s="3">
         <v>6</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>233.96985989999999</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="8">
         <v>217.51511210000001</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="8">
         <v>164.3015446</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="8">
         <v>163.2373312</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="8">
         <v>131.78678919999999</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="4">
         <v>84.65</v>
       </c>
       <c r="J14" s="3"/>
@@ -929,7 +976,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B15" s="3">
         <v>86.62</v>
@@ -937,22 +984,22 @@
       <c r="C15" s="3">
         <v>6</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>170.35396030000001</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="8">
         <v>158.10448980000001</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="8">
         <v>120.501402</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="8">
         <v>122.9810325</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="8">
         <v>100.43089550000001</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="4">
         <v>66.989999999999995</v>
       </c>
       <c r="J15" s="3"/>
@@ -963,7 +1010,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B16" s="3">
         <v>71.89</v>
@@ -971,22 +1018,22 @@
       <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>144.6873507</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="8">
         <v>133.65473979999999</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="8">
         <v>97.824027490000006</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="8">
         <v>102.15345910000001</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="8">
         <v>82.816393360000006</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="4">
         <v>53.39</v>
       </c>
       <c r="J16" s="3"/>
@@ -997,7 +1044,7 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" s="3">
         <v>66.650000000000006</v>
@@ -1005,22 +1052,22 @@
       <c r="C17" s="3">
         <v>6</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <v>124.782613</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="8">
         <v>115.24166870000001</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="8">
         <v>85.722657949999999</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="8">
         <v>90.017494260000007</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="8">
         <v>73.355584910000005</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <v>48.66</v>
       </c>
       <c r="J17" s="3"/>
@@ -1030,28 +1077,65 @@
       <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2654</v>
+      </c>
+      <c r="C18" s="3">
+        <v>7</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2412.59</v>
+      </c>
+      <c r="E18" s="4">
+        <v>3955.47</v>
+      </c>
+      <c r="F18" s="4">
+        <v>20179.490000000002</v>
+      </c>
+      <c r="G18" s="4">
+        <v>10608.2</v>
+      </c>
+      <c r="H18" s="4">
+        <v>2664.96</v>
+      </c>
+      <c r="I18" s="4">
+        <v>935.46</v>
+      </c>
       <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3">
+        <v>3300</v>
+      </c>
+      <c r="C19" s="3">
+        <v>7</v>
+      </c>
+      <c r="D19" s="4">
+        <v>4596.05</v>
+      </c>
+      <c r="E19" s="4">
+        <v>9505.6299999999992</v>
+      </c>
+      <c r="F19" s="4">
+        <v>52415.66</v>
+      </c>
+      <c r="G19" s="4">
+        <v>10914.11</v>
+      </c>
+      <c r="H19" s="4">
+        <v>32097.47</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1061,15 +1145,33 @@
       <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="C20" s="3">
+        <v>7</v>
+      </c>
+      <c r="D20" s="4">
+        <v>4290</v>
+      </c>
+      <c r="E20" s="4">
+        <v>9738</v>
+      </c>
+      <c r="F20" s="4">
+        <v>6156</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2226</v>
+      </c>
+      <c r="H20" s="4">
+        <v>3131</v>
+      </c>
+      <c r="I20" s="3">
+        <v>620</v>
+      </c>
       <c r="J20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -1096,12 +1198,6 @@
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -1398,7 +1494,8 @@
       <c r="O39" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/example_data/data_sum/electroopitcal.xlsx
+++ b/example_data/data_sum/electroopitcal.xlsx
@@ -1367,33 +1367,17 @@
       <c r="O30" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="16.5">
-      <c r="A31" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="8">
-        <v>2654</v>
-      </c>
-      <c r="C31" s="8">
-        <v>2</v>
-      </c>
-      <c r="D31" s="9">
-        <v>2412.59</v>
-      </c>
-      <c r="E31" s="9">
-        <v>3955.47</v>
-      </c>
-      <c r="F31" s="9">
-        <v>20179.49</v>
-      </c>
-      <c r="G31" s="9">
-        <v>10608.2</v>
-      </c>
-      <c r="H31" s="9">
-        <v>2664.96</v>
-      </c>
-      <c r="I31" s="9">
-        <v>935.46</v>
-      </c>
+      <c r="A31" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
